--- a/data/tags/סינגלים חדשים/sites/mizrahit/2026-03-week02/titles.xlsx
+++ b/data/tags/סינגלים חדשים/sites/mizrahit/2026-03-week02/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L11"/>
+  <dimension ref="A1:L20"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -436,16 +436,16 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>שי גז &amp; אברהם לוי - חדש בכל רגע</v>
+        <v>מיקה משה &amp; הלהקות הצבאיות - אומץ</v>
       </c>
       <c r="B2" t="str">
-        <v>2026-03-08</v>
+        <v>2026-03-09</v>
       </c>
       <c r="C2" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409912&amp;sid=9f3847199a1478c7dbbc018aa914d2d9</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409931&amp;sid=df4c3d4a5c70338b67ab2495eebc8a17</v>
       </c>
       <c r="D2" t="str">
-        <v>2026-03-08</v>
+        <v>2026-03-09</v>
       </c>
       <c r="E2" t="str">
         <v/>
@@ -469,21 +469,21 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>שי גז &amp; אברהם לוי - חדש בכל רגע</v>
+        <v>מיקה משה &amp; הלהקות הצבאיות - אומץ</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>נתנאל ששון - זה רשמי</v>
+        <v>להקת דרך - מונולוג מדינה ויראלי</v>
       </c>
       <c r="B3" t="str">
-        <v>2026-03-08</v>
+        <v>2026-03-09</v>
       </c>
       <c r="C3" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409911&amp;sid=9f3847199a1478c7dbbc018aa914d2d9</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409930&amp;sid=df4c3d4a5c70338b67ab2495eebc8a17</v>
       </c>
       <c r="D3" t="str">
-        <v>2026-03-08</v>
+        <v>2026-03-09</v>
       </c>
       <c r="E3" t="str">
         <v/>
@@ -507,21 +507,21 @@
         <v/>
       </c>
       <c r="L3" t="str">
-        <v>נתנאל ששון - זה רשמי</v>
+        <v>להקת דרך - מונולוג מדינה ויראלי</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>נתנאל אבקסיס - אין שום יאוש</v>
+        <v>דניאל זנדאני - יא יומה</v>
       </c>
       <c r="B4" t="str">
-        <v>2026-03-08</v>
+        <v>2026-03-09</v>
       </c>
       <c r="C4" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409910&amp;sid=9f3847199a1478c7dbbc018aa914d2d9</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409929&amp;sid=df4c3d4a5c70338b67ab2495eebc8a17</v>
       </c>
       <c r="D4" t="str">
-        <v>2026-03-08</v>
+        <v>2026-03-09</v>
       </c>
       <c r="E4" t="str">
         <v/>
@@ -545,21 +545,21 @@
         <v/>
       </c>
       <c r="L4" t="str">
-        <v>נתנאל אבקסיס - אין שום יאוש</v>
+        <v>דניאל זנדאני - יא יומה</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>נועם בתן - Michelle - השיר הרשמי של אירוויזיון 2026</v>
+        <v>פיקאסו - מתערבב לי</v>
       </c>
       <c r="B5" t="str">
-        <v>2026-03-08</v>
+        <v>2026-03-09</v>
       </c>
       <c r="C5" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409909&amp;sid=9f3847199a1478c7dbbc018aa914d2d9</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409928&amp;sid=df4c3d4a5c70338b67ab2495eebc8a17</v>
       </c>
       <c r="D5" t="str">
-        <v>2026-03-08</v>
+        <v>2026-03-09</v>
       </c>
       <c r="E5" t="str">
         <v/>
@@ -583,21 +583,21 @@
         <v/>
       </c>
       <c r="L5" t="str">
-        <v>נועם בתן - Michelle - השיר הרשמי של אירוויזיון 2026</v>
+        <v>פיקאסו - מתערבב לי</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>נהוראי רחמימוב &amp; אריאל מויאל - בוא ונרקוד</v>
+        <v>עמרי וקנין - שיר שלא נגמר</v>
       </c>
       <c r="B6" t="str">
-        <v>2026-03-08</v>
+        <v>2026-03-09</v>
       </c>
       <c r="C6" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409908&amp;sid=9f3847199a1478c7dbbc018aa914d2d9</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409927&amp;sid=df4c3d4a5c70338b67ab2495eebc8a17</v>
       </c>
       <c r="D6" t="str">
-        <v>2026-03-08</v>
+        <v>2026-03-09</v>
       </c>
       <c r="E6" t="str">
         <v/>
@@ -621,21 +621,21 @@
         <v/>
       </c>
       <c r="L6" t="str">
-        <v>נהוראי רחמימוב &amp; אריאל מויאל - בוא ונרקוד</v>
+        <v>עמרי וקנין - שיר שלא נגמר</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>מאיר רובין - הפצע בלב</v>
+        <v>נעם שפייר - כנות</v>
       </c>
       <c r="B7" t="str">
-        <v>2026-03-08</v>
+        <v>2026-03-09</v>
       </c>
       <c r="C7" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409907&amp;sid=9f3847199a1478c7dbbc018aa914d2d9</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409926&amp;sid=df4c3d4a5c70338b67ab2495eebc8a17</v>
       </c>
       <c r="D7" t="str">
-        <v>2026-03-08</v>
+        <v>2026-03-09</v>
       </c>
       <c r="E7" t="str">
         <v/>
@@ -659,21 +659,21 @@
         <v/>
       </c>
       <c r="L7" t="str">
-        <v>מאיר רובין - הפצע בלב</v>
+        <v>נעם שפייר - כנות</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>טליה אלפסי - מדבר ושותק</v>
+        <v>ישי ריבו - הנשמה לא Meta</v>
       </c>
       <c r="B8" t="str">
-        <v>2026-03-08</v>
+        <v>2026-03-09</v>
       </c>
       <c r="C8" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409906&amp;sid=9f3847199a1478c7dbbc018aa914d2d9</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409925&amp;sid=df4c3d4a5c70338b67ab2495eebc8a17</v>
       </c>
       <c r="D8" t="str">
-        <v>2026-03-08</v>
+        <v>2026-03-09</v>
       </c>
       <c r="E8" t="str">
         <v/>
@@ -697,21 +697,21 @@
         <v/>
       </c>
       <c r="L8" t="str">
-        <v>טליה אלפסי - מדבר ושותק</v>
+        <v>ישי ריבו - הנשמה לא Meta</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>חגית אסולין - שמש כבויה</v>
+        <v>יחיאל ליכטיגר - חוזרים לאבא</v>
       </c>
       <c r="B9" t="str">
-        <v>2026-03-08</v>
+        <v>2026-03-09</v>
       </c>
       <c r="C9" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409905&amp;sid=9f3847199a1478c7dbbc018aa914d2d9</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409924&amp;sid=df4c3d4a5c70338b67ab2495eebc8a17</v>
       </c>
       <c r="D9" t="str">
-        <v>2026-03-08</v>
+        <v>2026-03-09</v>
       </c>
       <c r="E9" t="str">
         <v/>
@@ -735,21 +735,21 @@
         <v/>
       </c>
       <c r="L9" t="str">
-        <v>חגית אסולין - שמש כבויה</v>
+        <v>יחיאל ליכטיגר - חוזרים לאבא</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>אורי אילן סבח - מחרוזת סוד האהבה 2026</v>
+        <v>יונתן שחר - דרך לחזור</v>
       </c>
       <c r="B10" t="str">
-        <v>2026-03-08</v>
+        <v>2026-03-09</v>
       </c>
       <c r="C10" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409904&amp;sid=9f3847199a1478c7dbbc018aa914d2d9</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409923&amp;sid=df4c3d4a5c70338b67ab2495eebc8a17</v>
       </c>
       <c r="D10" t="str">
-        <v>2026-03-08</v>
+        <v>2026-03-09</v>
       </c>
       <c r="E10" t="str">
         <v/>
@@ -773,21 +773,21 @@
         <v/>
       </c>
       <c r="L10" t="str">
-        <v>אורי אילן סבח - מחרוזת סוד האהבה 2026</v>
+        <v>יונתן שחר - דרך לחזור</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>אבישי - מזמור לתודה</v>
+        <v>יוחאי בן אב"י - וארשתיך לי</v>
       </c>
       <c r="B11" t="str">
-        <v>2026-03-08</v>
+        <v>2026-03-09</v>
       </c>
       <c r="C11" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409903&amp;sid=9f3847199a1478c7dbbc018aa914d2d9</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409922&amp;sid=df4c3d4a5c70338b67ab2495eebc8a17</v>
       </c>
       <c r="D11" t="str">
-        <v>2026-03-08</v>
+        <v>2026-03-09</v>
       </c>
       <c r="E11" t="str">
         <v/>
@@ -811,12 +811,354 @@
         <v/>
       </c>
       <c r="L11" t="str">
-        <v>אבישי - מזמור לתודה</v>
+        <v>יוחאי בן אב"י - וארשתיך לי</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>יובל אבידן - ברוך השם אני טוב</v>
+      </c>
+      <c r="B12" t="str">
+        <v>2026-03-09</v>
+      </c>
+      <c r="C12" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409921&amp;sid=df4c3d4a5c70338b67ab2495eebc8a17</v>
+      </c>
+      <c r="D12" t="str">
+        <v>2026-03-09</v>
+      </c>
+      <c r="E12" t="str">
+        <v/>
+      </c>
+      <c r="F12" t="str">
+        <v/>
+      </c>
+      <c r="G12" t="str">
+        <v/>
+      </c>
+      <c r="H12" t="str">
+        <v/>
+      </c>
+      <c r="I12" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J12" t="str">
+        <v/>
+      </c>
+      <c r="K12" t="str">
+        <v/>
+      </c>
+      <c r="L12" t="str">
+        <v>יובל אבידן - ברוך השם אני טוב</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>חני מסלה - פאבלות</v>
+      </c>
+      <c r="B13" t="str">
+        <v>2026-03-09</v>
+      </c>
+      <c r="C13" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409920&amp;sid=df4c3d4a5c70338b67ab2495eebc8a17</v>
+      </c>
+      <c r="D13" t="str">
+        <v>2026-03-09</v>
+      </c>
+      <c r="E13" t="str">
+        <v/>
+      </c>
+      <c r="F13" t="str">
+        <v/>
+      </c>
+      <c r="G13" t="str">
+        <v/>
+      </c>
+      <c r="H13" t="str">
+        <v/>
+      </c>
+      <c r="I13" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J13" t="str">
+        <v/>
+      </c>
+      <c r="K13" t="str">
+        <v/>
+      </c>
+      <c r="L13" t="str">
+        <v>חני מסלה - פאבלות</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="str">
+        <v>הילה גדסי - רק אתה יודע</v>
+      </c>
+      <c r="B14" t="str">
+        <v>2026-03-09</v>
+      </c>
+      <c r="C14" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409919&amp;sid=df4c3d4a5c70338b67ab2495eebc8a17</v>
+      </c>
+      <c r="D14" t="str">
+        <v>2026-03-09</v>
+      </c>
+      <c r="E14" t="str">
+        <v/>
+      </c>
+      <c r="F14" t="str">
+        <v/>
+      </c>
+      <c r="G14" t="str">
+        <v/>
+      </c>
+      <c r="H14" t="str">
+        <v/>
+      </c>
+      <c r="I14" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J14" t="str">
+        <v/>
+      </c>
+      <c r="K14" t="str">
+        <v/>
+      </c>
+      <c r="L14" t="str">
+        <v>הילה גדסי - רק אתה יודע</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="str">
+        <v>האחים בכר - נשאר הגעגוע</v>
+      </c>
+      <c r="B15" t="str">
+        <v>2026-03-09</v>
+      </c>
+      <c r="C15" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409918&amp;sid=df4c3d4a5c70338b67ab2495eebc8a17</v>
+      </c>
+      <c r="D15" t="str">
+        <v>2026-03-09</v>
+      </c>
+      <c r="E15" t="str">
+        <v/>
+      </c>
+      <c r="F15" t="str">
+        <v/>
+      </c>
+      <c r="G15" t="str">
+        <v/>
+      </c>
+      <c r="H15" t="str">
+        <v/>
+      </c>
+      <c r="I15" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J15" t="str">
+        <v/>
+      </c>
+      <c r="K15" t="str">
+        <v/>
+      </c>
+      <c r="L15" t="str">
+        <v>האחים בכר - נשאר הגעגוע</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="str">
+        <v>דניאל כהן - ימים של גאולה</v>
+      </c>
+      <c r="B16" t="str">
+        <v>2026-03-09</v>
+      </c>
+      <c r="C16" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409917&amp;sid=df4c3d4a5c70338b67ab2495eebc8a17</v>
+      </c>
+      <c r="D16" t="str">
+        <v>2026-03-09</v>
+      </c>
+      <c r="E16" t="str">
+        <v/>
+      </c>
+      <c r="F16" t="str">
+        <v/>
+      </c>
+      <c r="G16" t="str">
+        <v/>
+      </c>
+      <c r="H16" t="str">
+        <v/>
+      </c>
+      <c r="I16" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J16" t="str">
+        <v/>
+      </c>
+      <c r="K16" t="str">
+        <v/>
+      </c>
+      <c r="L16" t="str">
+        <v>דניאל כהן - ימים של גאולה</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="str">
+        <v>דילן דרור &amp; ויק אוחנה - יד על הלב</v>
+      </c>
+      <c r="B17" t="str">
+        <v>2026-03-09</v>
+      </c>
+      <c r="C17" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409916&amp;sid=df4c3d4a5c70338b67ab2495eebc8a17</v>
+      </c>
+      <c r="D17" t="str">
+        <v>2026-03-09</v>
+      </c>
+      <c r="E17" t="str">
+        <v/>
+      </c>
+      <c r="F17" t="str">
+        <v/>
+      </c>
+      <c r="G17" t="str">
+        <v/>
+      </c>
+      <c r="H17" t="str">
+        <v/>
+      </c>
+      <c r="I17" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J17" t="str">
+        <v/>
+      </c>
+      <c r="K17" t="str">
+        <v/>
+      </c>
+      <c r="L17" t="str">
+        <v>דילן דרור &amp; ויק אוחנה - יד על הלב</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="str">
+        <v>דוד חיים - מחרוזת שירי פורים 2026</v>
+      </c>
+      <c r="B18" t="str">
+        <v>2026-03-09</v>
+      </c>
+      <c r="C18" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409915&amp;sid=df4c3d4a5c70338b67ab2495eebc8a17</v>
+      </c>
+      <c r="D18" t="str">
+        <v>2026-03-09</v>
+      </c>
+      <c r="E18" t="str">
+        <v/>
+      </c>
+      <c r="F18" t="str">
+        <v/>
+      </c>
+      <c r="G18" t="str">
+        <v/>
+      </c>
+      <c r="H18" t="str">
+        <v/>
+      </c>
+      <c r="I18" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J18" t="str">
+        <v/>
+      </c>
+      <c r="K18" t="str">
+        <v/>
+      </c>
+      <c r="L18" t="str">
+        <v>דוד חיים - מחרוזת שירי פורים 2026</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="str">
+        <v>בנאל בן ציון - שיכור עם געגוע</v>
+      </c>
+      <c r="B19" t="str">
+        <v>2026-03-09</v>
+      </c>
+      <c r="C19" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409914&amp;sid=df4c3d4a5c70338b67ab2495eebc8a17</v>
+      </c>
+      <c r="D19" t="str">
+        <v>2026-03-09</v>
+      </c>
+      <c r="E19" t="str">
+        <v/>
+      </c>
+      <c r="F19" t="str">
+        <v/>
+      </c>
+      <c r="G19" t="str">
+        <v/>
+      </c>
+      <c r="H19" t="str">
+        <v/>
+      </c>
+      <c r="I19" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J19" t="str">
+        <v/>
+      </c>
+      <c r="K19" t="str">
+        <v/>
+      </c>
+      <c r="L19" t="str">
+        <v>בנאל בן ציון - שיכור עם געגוע</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="str">
+        <v>בן זוהר - טיל</v>
+      </c>
+      <c r="B20" t="str">
+        <v>2026-03-09</v>
+      </c>
+      <c r="C20" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409913&amp;sid=df4c3d4a5c70338b67ab2495eebc8a17</v>
+      </c>
+      <c r="D20" t="str">
+        <v>2026-03-09</v>
+      </c>
+      <c r="E20" t="str">
+        <v/>
+      </c>
+      <c r="F20" t="str">
+        <v/>
+      </c>
+      <c r="G20" t="str">
+        <v/>
+      </c>
+      <c r="H20" t="str">
+        <v/>
+      </c>
+      <c r="I20" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J20" t="str">
+        <v/>
+      </c>
+      <c r="K20" t="str">
+        <v/>
+      </c>
+      <c r="L20" t="str">
+        <v>בן זוהר - טיל</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L11"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L20"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/tags/סינגלים חדשים/sites/mizrahit/2026-03-week02/titles.xlsx
+++ b/data/tags/סינגלים חדשים/sites/mizrahit/2026-03-week02/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L20"/>
+  <dimension ref="A1:L11"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -436,16 +436,16 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>מיקה משה &amp; הלהקות הצבאיות - אומץ</v>
+        <v>שמעון לוי &amp; עמירן דביר - להיות אהוב</v>
       </c>
       <c r="B2" t="str">
-        <v>2026-03-09</v>
+        <v>2026-03-10</v>
       </c>
       <c r="C2" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409931&amp;sid=df4c3d4a5c70338b67ab2495eebc8a17</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409951&amp;sid=c993e7361615b1dd2d8db723e753315e</v>
       </c>
       <c r="D2" t="str">
-        <v>2026-03-09</v>
+        <v>2026-03-10</v>
       </c>
       <c r="E2" t="str">
         <v/>
@@ -469,21 +469,21 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>מיקה משה &amp; הלהקות הצבאיות - אומץ</v>
+        <v>שמעון לוי &amp; עמירן דביר - להיות אהוב</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>להקת דרך - מונולוג מדינה ויראלי</v>
+        <v>שמעון לוי - אהבת השם</v>
       </c>
       <c r="B3" t="str">
-        <v>2026-03-09</v>
+        <v>2026-03-10</v>
       </c>
       <c r="C3" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409930&amp;sid=df4c3d4a5c70338b67ab2495eebc8a17</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409950&amp;sid=c993e7361615b1dd2d8db723e753315e</v>
       </c>
       <c r="D3" t="str">
-        <v>2026-03-09</v>
+        <v>2026-03-10</v>
       </c>
       <c r="E3" t="str">
         <v/>
@@ -507,21 +507,21 @@
         <v/>
       </c>
       <c r="L3" t="str">
-        <v>להקת דרך - מונולוג מדינה ויראלי</v>
+        <v>שמעון לוי - אהבת השם</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>דניאל זנדאני - יא יומה</v>
+        <v>רפא' - יהודי</v>
       </c>
       <c r="B4" t="str">
-        <v>2026-03-09</v>
+        <v>2026-03-10</v>
       </c>
       <c r="C4" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409929&amp;sid=df4c3d4a5c70338b67ab2495eebc8a17</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409949&amp;sid=c993e7361615b1dd2d8db723e753315e</v>
       </c>
       <c r="D4" t="str">
-        <v>2026-03-09</v>
+        <v>2026-03-10</v>
       </c>
       <c r="E4" t="str">
         <v/>
@@ -545,21 +545,21 @@
         <v/>
       </c>
       <c r="L4" t="str">
-        <v>דניאל זנדאני - יא יומה</v>
+        <v>רפא' - יהודי</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>פיקאסו - מתערבב לי</v>
+        <v>ריעות זלאיט - חלום</v>
       </c>
       <c r="B5" t="str">
-        <v>2026-03-09</v>
+        <v>2026-03-10</v>
       </c>
       <c r="C5" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409928&amp;sid=df4c3d4a5c70338b67ab2495eebc8a17</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409948&amp;sid=c993e7361615b1dd2d8db723e753315e</v>
       </c>
       <c r="D5" t="str">
-        <v>2026-03-09</v>
+        <v>2026-03-10</v>
       </c>
       <c r="E5" t="str">
         <v/>
@@ -583,21 +583,21 @@
         <v/>
       </c>
       <c r="L5" t="str">
-        <v>פיקאסו - מתערבב לי</v>
+        <v>ריעות זלאיט - חלום</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>עמרי וקנין - שיר שלא נגמר</v>
+        <v>סאליאור פטיטו - בין הכיסאות</v>
       </c>
       <c r="B6" t="str">
-        <v>2026-03-09</v>
+        <v>2026-03-10</v>
       </c>
       <c r="C6" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409927&amp;sid=df4c3d4a5c70338b67ab2495eebc8a17</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409947&amp;sid=c993e7361615b1dd2d8db723e753315e</v>
       </c>
       <c r="D6" t="str">
-        <v>2026-03-09</v>
+        <v>2026-03-10</v>
       </c>
       <c r="E6" t="str">
         <v/>
@@ -621,21 +621,21 @@
         <v/>
       </c>
       <c r="L6" t="str">
-        <v>עמרי וקנין - שיר שלא נגמר</v>
+        <v>סאליאור פטיטו - בין הכיסאות</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>נעם שפייר - כנות</v>
+        <v>ליאם גולן - להיות רק בשמחה</v>
       </c>
       <c r="B7" t="str">
-        <v>2026-03-09</v>
+        <v>2026-03-10</v>
       </c>
       <c r="C7" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409926&amp;sid=df4c3d4a5c70338b67ab2495eebc8a17</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409946&amp;sid=c993e7361615b1dd2d8db723e753315e</v>
       </c>
       <c r="D7" t="str">
-        <v>2026-03-09</v>
+        <v>2026-03-10</v>
       </c>
       <c r="E7" t="str">
         <v/>
@@ -659,21 +659,21 @@
         <v/>
       </c>
       <c r="L7" t="str">
-        <v>נעם שפייר - כנות</v>
+        <v>ליאם גולן - להיות רק בשמחה</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>ישי ריבו - הנשמה לא Meta</v>
+        <v>יוסי פריד - מחרוזת שבת 2026</v>
       </c>
       <c r="B8" t="str">
-        <v>2026-03-09</v>
+        <v>2026-03-10</v>
       </c>
       <c r="C8" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409925&amp;sid=df4c3d4a5c70338b67ab2495eebc8a17</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409945&amp;sid=c993e7361615b1dd2d8db723e753315e</v>
       </c>
       <c r="D8" t="str">
-        <v>2026-03-09</v>
+        <v>2026-03-10</v>
       </c>
       <c r="E8" t="str">
         <v/>
@@ -697,21 +697,21 @@
         <v/>
       </c>
       <c r="L8" t="str">
-        <v>ישי ריבו - הנשמה לא Meta</v>
+        <v>יוסי פריד - מחרוזת שבת 2026</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>יחיאל ליכטיגר - חוזרים לאבא</v>
+        <v>אורן כדורי - אמא מה עושים</v>
       </c>
       <c r="B9" t="str">
-        <v>2026-03-09</v>
+        <v>2026-03-10</v>
       </c>
       <c r="C9" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409924&amp;sid=df4c3d4a5c70338b67ab2495eebc8a17</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409944&amp;sid=c993e7361615b1dd2d8db723e753315e</v>
       </c>
       <c r="D9" t="str">
-        <v>2026-03-09</v>
+        <v>2026-03-10</v>
       </c>
       <c r="E9" t="str">
         <v/>
@@ -735,21 +735,21 @@
         <v/>
       </c>
       <c r="L9" t="str">
-        <v>יחיאל ליכטיגר - חוזרים לאבא</v>
+        <v>אורן כדורי - אמא מה עושים</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>יונתן שחר - דרך לחזור</v>
+        <v>אופיר אלחייני - שדה שושנים</v>
       </c>
       <c r="B10" t="str">
-        <v>2026-03-09</v>
+        <v>2026-03-10</v>
       </c>
       <c r="C10" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409923&amp;sid=df4c3d4a5c70338b67ab2495eebc8a17</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409943&amp;sid=c993e7361615b1dd2d8db723e753315e</v>
       </c>
       <c r="D10" t="str">
-        <v>2026-03-09</v>
+        <v>2026-03-10</v>
       </c>
       <c r="E10" t="str">
         <v/>
@@ -773,21 +773,21 @@
         <v/>
       </c>
       <c r="L10" t="str">
-        <v>יונתן שחר - דרך לחזור</v>
+        <v>אופיר אלחייני - שדה שושנים</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>יוחאי בן אב"י - וארשתיך לי</v>
+        <v>אברימי רוט - יצא אדם</v>
       </c>
       <c r="B11" t="str">
-        <v>2026-03-09</v>
+        <v>2026-03-10</v>
       </c>
       <c r="C11" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409922&amp;sid=df4c3d4a5c70338b67ab2495eebc8a17</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409942&amp;sid=c993e7361615b1dd2d8db723e753315e</v>
       </c>
       <c r="D11" t="str">
-        <v>2026-03-09</v>
+        <v>2026-03-10</v>
       </c>
       <c r="E11" t="str">
         <v/>
@@ -811,354 +811,12 @@
         <v/>
       </c>
       <c r="L11" t="str">
-        <v>יוחאי בן אב"י - וארשתיך לי</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="str">
-        <v>יובל אבידן - ברוך השם אני טוב</v>
-      </c>
-      <c r="B12" t="str">
-        <v>2026-03-09</v>
-      </c>
-      <c r="C12" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409921&amp;sid=df4c3d4a5c70338b67ab2495eebc8a17</v>
-      </c>
-      <c r="D12" t="str">
-        <v>2026-03-09</v>
-      </c>
-      <c r="E12" t="str">
-        <v/>
-      </c>
-      <c r="F12" t="str">
-        <v/>
-      </c>
-      <c r="G12" t="str">
-        <v/>
-      </c>
-      <c r="H12" t="str">
-        <v/>
-      </c>
-      <c r="I12" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J12" t="str">
-        <v/>
-      </c>
-      <c r="K12" t="str">
-        <v/>
-      </c>
-      <c r="L12" t="str">
-        <v>יובל אבידן - ברוך השם אני טוב</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="str">
-        <v>חני מסלה - פאבלות</v>
-      </c>
-      <c r="B13" t="str">
-        <v>2026-03-09</v>
-      </c>
-      <c r="C13" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409920&amp;sid=df4c3d4a5c70338b67ab2495eebc8a17</v>
-      </c>
-      <c r="D13" t="str">
-        <v>2026-03-09</v>
-      </c>
-      <c r="E13" t="str">
-        <v/>
-      </c>
-      <c r="F13" t="str">
-        <v/>
-      </c>
-      <c r="G13" t="str">
-        <v/>
-      </c>
-      <c r="H13" t="str">
-        <v/>
-      </c>
-      <c r="I13" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J13" t="str">
-        <v/>
-      </c>
-      <c r="K13" t="str">
-        <v/>
-      </c>
-      <c r="L13" t="str">
-        <v>חני מסלה - פאבלות</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="str">
-        <v>הילה גדסי - רק אתה יודע</v>
-      </c>
-      <c r="B14" t="str">
-        <v>2026-03-09</v>
-      </c>
-      <c r="C14" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409919&amp;sid=df4c3d4a5c70338b67ab2495eebc8a17</v>
-      </c>
-      <c r="D14" t="str">
-        <v>2026-03-09</v>
-      </c>
-      <c r="E14" t="str">
-        <v/>
-      </c>
-      <c r="F14" t="str">
-        <v/>
-      </c>
-      <c r="G14" t="str">
-        <v/>
-      </c>
-      <c r="H14" t="str">
-        <v/>
-      </c>
-      <c r="I14" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J14" t="str">
-        <v/>
-      </c>
-      <c r="K14" t="str">
-        <v/>
-      </c>
-      <c r="L14" t="str">
-        <v>הילה גדסי - רק אתה יודע</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="str">
-        <v>האחים בכר - נשאר הגעגוע</v>
-      </c>
-      <c r="B15" t="str">
-        <v>2026-03-09</v>
-      </c>
-      <c r="C15" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409918&amp;sid=df4c3d4a5c70338b67ab2495eebc8a17</v>
-      </c>
-      <c r="D15" t="str">
-        <v>2026-03-09</v>
-      </c>
-      <c r="E15" t="str">
-        <v/>
-      </c>
-      <c r="F15" t="str">
-        <v/>
-      </c>
-      <c r="G15" t="str">
-        <v/>
-      </c>
-      <c r="H15" t="str">
-        <v/>
-      </c>
-      <c r="I15" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J15" t="str">
-        <v/>
-      </c>
-      <c r="K15" t="str">
-        <v/>
-      </c>
-      <c r="L15" t="str">
-        <v>האחים בכר - נשאר הגעגוע</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="str">
-        <v>דניאל כהן - ימים של גאולה</v>
-      </c>
-      <c r="B16" t="str">
-        <v>2026-03-09</v>
-      </c>
-      <c r="C16" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409917&amp;sid=df4c3d4a5c70338b67ab2495eebc8a17</v>
-      </c>
-      <c r="D16" t="str">
-        <v>2026-03-09</v>
-      </c>
-      <c r="E16" t="str">
-        <v/>
-      </c>
-      <c r="F16" t="str">
-        <v/>
-      </c>
-      <c r="G16" t="str">
-        <v/>
-      </c>
-      <c r="H16" t="str">
-        <v/>
-      </c>
-      <c r="I16" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J16" t="str">
-        <v/>
-      </c>
-      <c r="K16" t="str">
-        <v/>
-      </c>
-      <c r="L16" t="str">
-        <v>דניאל כהן - ימים של גאולה</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="str">
-        <v>דילן דרור &amp; ויק אוחנה - יד על הלב</v>
-      </c>
-      <c r="B17" t="str">
-        <v>2026-03-09</v>
-      </c>
-      <c r="C17" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409916&amp;sid=df4c3d4a5c70338b67ab2495eebc8a17</v>
-      </c>
-      <c r="D17" t="str">
-        <v>2026-03-09</v>
-      </c>
-      <c r="E17" t="str">
-        <v/>
-      </c>
-      <c r="F17" t="str">
-        <v/>
-      </c>
-      <c r="G17" t="str">
-        <v/>
-      </c>
-      <c r="H17" t="str">
-        <v/>
-      </c>
-      <c r="I17" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J17" t="str">
-        <v/>
-      </c>
-      <c r="K17" t="str">
-        <v/>
-      </c>
-      <c r="L17" t="str">
-        <v>דילן דרור &amp; ויק אוחנה - יד על הלב</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="str">
-        <v>דוד חיים - מחרוזת שירי פורים 2026</v>
-      </c>
-      <c r="B18" t="str">
-        <v>2026-03-09</v>
-      </c>
-      <c r="C18" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409915&amp;sid=df4c3d4a5c70338b67ab2495eebc8a17</v>
-      </c>
-      <c r="D18" t="str">
-        <v>2026-03-09</v>
-      </c>
-      <c r="E18" t="str">
-        <v/>
-      </c>
-      <c r="F18" t="str">
-        <v/>
-      </c>
-      <c r="G18" t="str">
-        <v/>
-      </c>
-      <c r="H18" t="str">
-        <v/>
-      </c>
-      <c r="I18" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J18" t="str">
-        <v/>
-      </c>
-      <c r="K18" t="str">
-        <v/>
-      </c>
-      <c r="L18" t="str">
-        <v>דוד חיים - מחרוזת שירי פורים 2026</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="str">
-        <v>בנאל בן ציון - שיכור עם געגוע</v>
-      </c>
-      <c r="B19" t="str">
-        <v>2026-03-09</v>
-      </c>
-      <c r="C19" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409914&amp;sid=df4c3d4a5c70338b67ab2495eebc8a17</v>
-      </c>
-      <c r="D19" t="str">
-        <v>2026-03-09</v>
-      </c>
-      <c r="E19" t="str">
-        <v/>
-      </c>
-      <c r="F19" t="str">
-        <v/>
-      </c>
-      <c r="G19" t="str">
-        <v/>
-      </c>
-      <c r="H19" t="str">
-        <v/>
-      </c>
-      <c r="I19" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J19" t="str">
-        <v/>
-      </c>
-      <c r="K19" t="str">
-        <v/>
-      </c>
-      <c r="L19" t="str">
-        <v>בנאל בן ציון - שיכור עם געגוע</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="str">
-        <v>בן זוהר - טיל</v>
-      </c>
-      <c r="B20" t="str">
-        <v>2026-03-09</v>
-      </c>
-      <c r="C20" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409913&amp;sid=df4c3d4a5c70338b67ab2495eebc8a17</v>
-      </c>
-      <c r="D20" t="str">
-        <v>2026-03-09</v>
-      </c>
-      <c r="E20" t="str">
-        <v/>
-      </c>
-      <c r="F20" t="str">
-        <v/>
-      </c>
-      <c r="G20" t="str">
-        <v/>
-      </c>
-      <c r="H20" t="str">
-        <v/>
-      </c>
-      <c r="I20" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J20" t="str">
-        <v/>
-      </c>
-      <c r="K20" t="str">
-        <v/>
-      </c>
-      <c r="L20" t="str">
-        <v>בן זוהר - טיל</v>
+        <v>אברימי רוט - יצא אדם</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L20"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L11"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/tags/סינגלים חדשים/sites/mizrahit/2026-03-week02/titles.xlsx
+++ b/data/tags/סינגלים חדשים/sites/mizrahit/2026-03-week02/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L11"/>
+  <dimension ref="A1:L8"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -436,16 +436,16 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>שמעון לוי &amp; עמירן דביר - להיות אהוב</v>
+        <v>אלחנן ענבל - מלאך</v>
       </c>
       <c r="B2" t="str">
-        <v>2026-03-10</v>
+        <v>2026-03-11</v>
       </c>
       <c r="C2" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409951&amp;sid=c993e7361615b1dd2d8db723e753315e</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409958&amp;sid=19f2269f6a7663d13b7ea33c9809090c</v>
       </c>
       <c r="D2" t="str">
-        <v>2026-03-10</v>
+        <v>2026-03-11</v>
       </c>
       <c r="E2" t="str">
         <v/>
@@ -469,21 +469,21 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>שמעון לוי &amp; עמירן דביר - להיות אהוב</v>
+        <v>אלחנן ענבל - מלאך</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>שמעון לוי - אהבת השם</v>
+        <v>איציק דדיה - יצר טוב</v>
       </c>
       <c r="B3" t="str">
-        <v>2026-03-10</v>
+        <v>2026-03-11</v>
       </c>
       <c r="C3" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409950&amp;sid=c993e7361615b1dd2d8db723e753315e</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409957&amp;sid=19f2269f6a7663d13b7ea33c9809090c</v>
       </c>
       <c r="D3" t="str">
-        <v>2026-03-10</v>
+        <v>2026-03-11</v>
       </c>
       <c r="E3" t="str">
         <v/>
@@ -507,21 +507,21 @@
         <v/>
       </c>
       <c r="L3" t="str">
-        <v>שמעון לוי - אהבת השם</v>
+        <v>איציק דדיה - יצר טוב</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>רפא' - יהודי</v>
+        <v>אייל סאלם - מחשבות</v>
       </c>
       <c r="B4" t="str">
-        <v>2026-03-10</v>
+        <v>2026-03-11</v>
       </c>
       <c r="C4" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409949&amp;sid=c993e7361615b1dd2d8db723e753315e</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409956&amp;sid=19f2269f6a7663d13b7ea33c9809090c</v>
       </c>
       <c r="D4" t="str">
-        <v>2026-03-10</v>
+        <v>2026-03-11</v>
       </c>
       <c r="E4" t="str">
         <v/>
@@ -545,21 +545,21 @@
         <v/>
       </c>
       <c r="L4" t="str">
-        <v>רפא' - יהודי</v>
+        <v>אייל סאלם - מחשבות</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>ריעות זלאיט - חלום</v>
+        <v>אור שושן &amp; מור סופר - זמן</v>
       </c>
       <c r="B5" t="str">
-        <v>2026-03-10</v>
+        <v>2026-03-11</v>
       </c>
       <c r="C5" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409948&amp;sid=c993e7361615b1dd2d8db723e753315e</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409955&amp;sid=19f2269f6a7663d13b7ea33c9809090c</v>
       </c>
       <c r="D5" t="str">
-        <v>2026-03-10</v>
+        <v>2026-03-11</v>
       </c>
       <c r="E5" t="str">
         <v/>
@@ -583,21 +583,21 @@
         <v/>
       </c>
       <c r="L5" t="str">
-        <v>ריעות זלאיט - חלום</v>
+        <v>אור שושן &amp; מור סופר - זמן</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>סאליאור פטיטו - בין הכיסאות</v>
+        <v>אברימי רוט - בשם המלך</v>
       </c>
       <c r="B6" t="str">
-        <v>2026-03-10</v>
+        <v>2026-03-11</v>
       </c>
       <c r="C6" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409947&amp;sid=c993e7361615b1dd2d8db723e753315e</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409954&amp;sid=19f2269f6a7663d13b7ea33c9809090c</v>
       </c>
       <c r="D6" t="str">
-        <v>2026-03-10</v>
+        <v>2026-03-11</v>
       </c>
       <c r="E6" t="str">
         <v/>
@@ -621,21 +621,21 @@
         <v/>
       </c>
       <c r="L6" t="str">
-        <v>סאליאור פטיטו - בין הכיסאות</v>
+        <v>אברימי רוט - בשם המלך</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>ליאם גולן - להיות רק בשמחה</v>
+        <v>אבי ביטר - לא מפחדים</v>
       </c>
       <c r="B7" t="str">
-        <v>2026-03-10</v>
+        <v>2026-03-11</v>
       </c>
       <c r="C7" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409946&amp;sid=c993e7361615b1dd2d8db723e753315e</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409953&amp;sid=19f2269f6a7663d13b7ea33c9809090c</v>
       </c>
       <c r="D7" t="str">
-        <v>2026-03-10</v>
+        <v>2026-03-11</v>
       </c>
       <c r="E7" t="str">
         <v/>
@@ -659,21 +659,21 @@
         <v/>
       </c>
       <c r="L7" t="str">
-        <v>ליאם גולן - להיות רק בשמחה</v>
+        <v>אבי ביטר - לא מפחדים</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>יוסי פריד - מחרוזת שבת 2026</v>
+        <v>Pure Spirit - מתגעגעת</v>
       </c>
       <c r="B8" t="str">
-        <v>2026-03-10</v>
+        <v>2026-03-11</v>
       </c>
       <c r="C8" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409945&amp;sid=c993e7361615b1dd2d8db723e753315e</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409952&amp;sid=19f2269f6a7663d13b7ea33c9809090c</v>
       </c>
       <c r="D8" t="str">
-        <v>2026-03-10</v>
+        <v>2026-03-11</v>
       </c>
       <c r="E8" t="str">
         <v/>
@@ -697,126 +697,12 @@
         <v/>
       </c>
       <c r="L8" t="str">
-        <v>יוסי פריד - מחרוזת שבת 2026</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="str">
-        <v>אורן כדורי - אמא מה עושים</v>
-      </c>
-      <c r="B9" t="str">
-        <v>2026-03-10</v>
-      </c>
-      <c r="C9" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409944&amp;sid=c993e7361615b1dd2d8db723e753315e</v>
-      </c>
-      <c r="D9" t="str">
-        <v>2026-03-10</v>
-      </c>
-      <c r="E9" t="str">
-        <v/>
-      </c>
-      <c r="F9" t="str">
-        <v/>
-      </c>
-      <c r="G9" t="str">
-        <v/>
-      </c>
-      <c r="H9" t="str">
-        <v/>
-      </c>
-      <c r="I9" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J9" t="str">
-        <v/>
-      </c>
-      <c r="K9" t="str">
-        <v/>
-      </c>
-      <c r="L9" t="str">
-        <v>אורן כדורי - אמא מה עושים</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="str">
-        <v>אופיר אלחייני - שדה שושנים</v>
-      </c>
-      <c r="B10" t="str">
-        <v>2026-03-10</v>
-      </c>
-      <c r="C10" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409943&amp;sid=c993e7361615b1dd2d8db723e753315e</v>
-      </c>
-      <c r="D10" t="str">
-        <v>2026-03-10</v>
-      </c>
-      <c r="E10" t="str">
-        <v/>
-      </c>
-      <c r="F10" t="str">
-        <v/>
-      </c>
-      <c r="G10" t="str">
-        <v/>
-      </c>
-      <c r="H10" t="str">
-        <v/>
-      </c>
-      <c r="I10" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J10" t="str">
-        <v/>
-      </c>
-      <c r="K10" t="str">
-        <v/>
-      </c>
-      <c r="L10" t="str">
-        <v>אופיר אלחייני - שדה שושנים</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="str">
-        <v>אברימי רוט - יצא אדם</v>
-      </c>
-      <c r="B11" t="str">
-        <v>2026-03-10</v>
-      </c>
-      <c r="C11" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409942&amp;sid=c993e7361615b1dd2d8db723e753315e</v>
-      </c>
-      <c r="D11" t="str">
-        <v>2026-03-10</v>
-      </c>
-      <c r="E11" t="str">
-        <v/>
-      </c>
-      <c r="F11" t="str">
-        <v/>
-      </c>
-      <c r="G11" t="str">
-        <v/>
-      </c>
-      <c r="H11" t="str">
-        <v/>
-      </c>
-      <c r="I11" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J11" t="str">
-        <v/>
-      </c>
-      <c r="K11" t="str">
-        <v/>
-      </c>
-      <c r="L11" t="str">
-        <v>אברימי רוט - יצא אדם</v>
+        <v>Pure Spirit - מתגעגעת</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L11"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L8"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/tags/סינגלים חדשים/sites/mizrahit/2026-03-week02/titles.xlsx
+++ b/data/tags/סינגלים חדשים/sites/mizrahit/2026-03-week02/titles.xlsx
@@ -436,13 +436,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>אלחנן ענבל - מלאך</v>
+        <v>שירז אברהם - אבא תודה</v>
       </c>
       <c r="B2" t="str">
         <v>2026-03-11</v>
       </c>
       <c r="C2" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409958&amp;sid=19f2269f6a7663d13b7ea33c9809090c</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409965&amp;sid=c58b90bdfe7aee15dc200715dd0102e0</v>
       </c>
       <c r="D2" t="str">
         <v>2026-03-11</v>
@@ -469,18 +469,18 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>אלחנן ענבל - מלאך</v>
+        <v>שירז אברהם - אבא תודה</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>איציק דדיה - יצר טוב</v>
+        <v>עמרי אלשוקני - מאשאפ שנות ה 90</v>
       </c>
       <c r="B3" t="str">
         <v>2026-03-11</v>
       </c>
       <c r="C3" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409957&amp;sid=19f2269f6a7663d13b7ea33c9809090c</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409964&amp;sid=c58b90bdfe7aee15dc200715dd0102e0</v>
       </c>
       <c r="D3" t="str">
         <v>2026-03-11</v>
@@ -507,18 +507,18 @@
         <v/>
       </c>
       <c r="L3" t="str">
-        <v>איציק דדיה - יצר טוב</v>
+        <v>עמרי אלשוקני - מאשאפ שנות ה 90</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>אייל סאלם - מחשבות</v>
+        <v>משה קליין &amp; דוד חפצדי - ואיך הימים</v>
       </c>
       <c r="B4" t="str">
         <v>2026-03-11</v>
       </c>
       <c r="C4" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409956&amp;sid=19f2269f6a7663d13b7ea33c9809090c</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409963&amp;sid=c58b90bdfe7aee15dc200715dd0102e0</v>
       </c>
       <c r="D4" t="str">
         <v>2026-03-11</v>
@@ -545,18 +545,18 @@
         <v/>
       </c>
       <c r="L4" t="str">
-        <v>אייל סאלם - מחשבות</v>
+        <v>משה קליין &amp; דוד חפצדי - ואיך הימים</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>אור שושן &amp; מור סופר - זמן</v>
+        <v>להקת דרך - אל תאמר</v>
       </c>
       <c r="B5" t="str">
         <v>2026-03-11</v>
       </c>
       <c r="C5" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409955&amp;sid=19f2269f6a7663d13b7ea33c9809090c</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409962&amp;sid=c58b90bdfe7aee15dc200715dd0102e0</v>
       </c>
       <c r="D5" t="str">
         <v>2026-03-11</v>
@@ -583,18 +583,18 @@
         <v/>
       </c>
       <c r="L5" t="str">
-        <v>אור שושן &amp; מור סופר - זמן</v>
+        <v>להקת דרך - אל תאמר</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>אברימי רוט - בשם המלך</v>
+        <v>יצחק אפרים קוך - ואני בחסדך בטחתי</v>
       </c>
       <c r="B6" t="str">
         <v>2026-03-11</v>
       </c>
       <c r="C6" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409954&amp;sid=19f2269f6a7663d13b7ea33c9809090c</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409961&amp;sid=c58b90bdfe7aee15dc200715dd0102e0</v>
       </c>
       <c r="D6" t="str">
         <v>2026-03-11</v>
@@ -621,18 +621,18 @@
         <v/>
       </c>
       <c r="L6" t="str">
-        <v>אברימי רוט - בשם המלך</v>
+        <v>יצחק אפרים קוך - ואני בחסדך בטחתי</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>אבי ביטר - לא מפחדים</v>
+        <v>יניב בן ישי - זאב בודד</v>
       </c>
       <c r="B7" t="str">
         <v>2026-03-11</v>
       </c>
       <c r="C7" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409953&amp;sid=19f2269f6a7663d13b7ea33c9809090c</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409960&amp;sid=c58b90bdfe7aee15dc200715dd0102e0</v>
       </c>
       <c r="D7" t="str">
         <v>2026-03-11</v>
@@ -659,18 +659,18 @@
         <v/>
       </c>
       <c r="L7" t="str">
-        <v>אבי ביטר - לא מפחדים</v>
+        <v>יניב בן ישי - זאב בודד</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>Pure Spirit - מתגעגעת</v>
+        <v>הרב יהודה חודדה - לכבוד חמדת לבבי 2026</v>
       </c>
       <c r="B8" t="str">
         <v>2026-03-11</v>
       </c>
       <c r="C8" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409952&amp;sid=19f2269f6a7663d13b7ea33c9809090c</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409959&amp;sid=c58b90bdfe7aee15dc200715dd0102e0</v>
       </c>
       <c r="D8" t="str">
         <v>2026-03-11</v>
@@ -697,7 +697,7 @@
         <v/>
       </c>
       <c r="L8" t="str">
-        <v>Pure Spirit - מתגעגעת</v>
+        <v>הרב יהודה חודדה - לכבוד חמדת לבבי 2026</v>
       </c>
     </row>
   </sheetData>

--- a/data/tags/סינגלים חדשים/sites/mizrahit/2026-03-week02/titles.xlsx
+++ b/data/tags/סינגלים חדשים/sites/mizrahit/2026-03-week02/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L8"/>
+  <dimension ref="A1:L9"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -436,16 +436,16 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>שירז אברהם - אבא תודה</v>
+        <v>דניאל חן - נפש תאומה</v>
       </c>
       <c r="B2" t="str">
-        <v>2026-03-11</v>
+        <v>2026-03-12</v>
       </c>
       <c r="C2" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409965&amp;sid=c58b90bdfe7aee15dc200715dd0102e0</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409973&amp;sid=9e7b7f175072edda36a8d7e9777610ff</v>
       </c>
       <c r="D2" t="str">
-        <v>2026-03-11</v>
+        <v>2026-03-12</v>
       </c>
       <c r="E2" t="str">
         <v/>
@@ -469,21 +469,21 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>שירז אברהם - אבא תודה</v>
+        <v>דניאל חן - נפש תאומה</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>עמרי אלשוקני - מאשאפ שנות ה 90</v>
+        <v>דנה זר - עוד סיבה</v>
       </c>
       <c r="B3" t="str">
-        <v>2026-03-11</v>
+        <v>2026-03-12</v>
       </c>
       <c r="C3" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409964&amp;sid=c58b90bdfe7aee15dc200715dd0102e0</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409972&amp;sid=9e7b7f175072edda36a8d7e9777610ff</v>
       </c>
       <c r="D3" t="str">
-        <v>2026-03-11</v>
+        <v>2026-03-12</v>
       </c>
       <c r="E3" t="str">
         <v/>
@@ -507,21 +507,21 @@
         <v/>
       </c>
       <c r="L3" t="str">
-        <v>עמרי אלשוקני - מאשאפ שנות ה 90</v>
+        <v>דנה זר - עוד סיבה</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>משה קליין &amp; דוד חפצדי - ואיך הימים</v>
+        <v>גל סבג - מחרוזת ברית 2026</v>
       </c>
       <c r="B4" t="str">
-        <v>2026-03-11</v>
+        <v>2026-03-12</v>
       </c>
       <c r="C4" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409963&amp;sid=c58b90bdfe7aee15dc200715dd0102e0</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409971&amp;sid=9e7b7f175072edda36a8d7e9777610ff</v>
       </c>
       <c r="D4" t="str">
-        <v>2026-03-11</v>
+        <v>2026-03-12</v>
       </c>
       <c r="E4" t="str">
         <v/>
@@ -545,21 +545,21 @@
         <v/>
       </c>
       <c r="L4" t="str">
-        <v>משה קליין &amp; דוד חפצדי - ואיך הימים</v>
+        <v>גל סבג - מחרוזת ברית 2026</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>להקת דרך - אל תאמר</v>
+        <v>ג’יין בורדו - חלמתי שאתה פה</v>
       </c>
       <c r="B5" t="str">
-        <v>2026-03-11</v>
+        <v>2026-03-12</v>
       </c>
       <c r="C5" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409962&amp;sid=c58b90bdfe7aee15dc200715dd0102e0</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409970&amp;sid=9e7b7f175072edda36a8d7e9777610ff</v>
       </c>
       <c r="D5" t="str">
-        <v>2026-03-11</v>
+        <v>2026-03-12</v>
       </c>
       <c r="E5" t="str">
         <v/>
@@ -583,21 +583,21 @@
         <v/>
       </c>
       <c r="L5" t="str">
-        <v>להקת דרך - אל תאמר</v>
+        <v>ג’יין בורדו - חלמתי שאתה פה</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>יצחק אפרים קוך - ואני בחסדך בטחתי</v>
+        <v>ארז יחיאל &amp; אלחנן בידני - כי אשמרה שבת</v>
       </c>
       <c r="B6" t="str">
-        <v>2026-03-11</v>
+        <v>2026-03-12</v>
       </c>
       <c r="C6" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409961&amp;sid=c58b90bdfe7aee15dc200715dd0102e0</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409969&amp;sid=9e7b7f175072edda36a8d7e9777610ff</v>
       </c>
       <c r="D6" t="str">
-        <v>2026-03-11</v>
+        <v>2026-03-12</v>
       </c>
       <c r="E6" t="str">
         <v/>
@@ -621,21 +621,21 @@
         <v/>
       </c>
       <c r="L6" t="str">
-        <v>יצחק אפרים קוך - ואני בחסדך בטחתי</v>
+        <v>ארז יחיאל &amp; אלחנן בידני - כי אשמרה שבת</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>יניב בן ישי - זאב בודד</v>
+        <v>איציק איזמירלי - לא אמרת</v>
       </c>
       <c r="B7" t="str">
-        <v>2026-03-11</v>
+        <v>2026-03-12</v>
       </c>
       <c r="C7" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409960&amp;sid=c58b90bdfe7aee15dc200715dd0102e0</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409968&amp;sid=9e7b7f175072edda36a8d7e9777610ff</v>
       </c>
       <c r="D7" t="str">
-        <v>2026-03-11</v>
+        <v>2026-03-12</v>
       </c>
       <c r="E7" t="str">
         <v/>
@@ -659,21 +659,21 @@
         <v/>
       </c>
       <c r="L7" t="str">
-        <v>יניב בן ישי - זאב בודד</v>
+        <v>איציק איזמירלי - לא אמרת</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>הרב יהודה חודדה - לכבוד חמדת לבבי 2026</v>
+        <v>אהרן בלעיש - תודה שאתה כאן</v>
       </c>
       <c r="B8" t="str">
-        <v>2026-03-11</v>
+        <v>2026-03-12</v>
       </c>
       <c r="C8" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409959&amp;sid=c58b90bdfe7aee15dc200715dd0102e0</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409967&amp;sid=9e7b7f175072edda36a8d7e9777610ff</v>
       </c>
       <c r="D8" t="str">
-        <v>2026-03-11</v>
+        <v>2026-03-12</v>
       </c>
       <c r="E8" t="str">
         <v/>
@@ -697,12 +697,50 @@
         <v/>
       </c>
       <c r="L8" t="str">
-        <v>הרב יהודה חודדה - לכבוד חמדת לבבי 2026</v>
+        <v>אהרן בלעיש - תודה שאתה כאן</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>אביב סטמס - דמעות על הכרית</v>
+      </c>
+      <c r="B9" t="str">
+        <v>2026-03-12</v>
+      </c>
+      <c r="C9" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409966&amp;sid=9e7b7f175072edda36a8d7e9777610ff</v>
+      </c>
+      <c r="D9" t="str">
+        <v>2026-03-12</v>
+      </c>
+      <c r="E9" t="str">
+        <v/>
+      </c>
+      <c r="F9" t="str">
+        <v/>
+      </c>
+      <c r="G9" t="str">
+        <v/>
+      </c>
+      <c r="H9" t="str">
+        <v/>
+      </c>
+      <c r="I9" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J9" t="str">
+        <v/>
+      </c>
+      <c r="K9" t="str">
+        <v/>
+      </c>
+      <c r="L9" t="str">
+        <v>אביב סטמס - דמעות על הכרית</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L8"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L9"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/tags/סינגלים חדשים/sites/mizrahit/2026-03-week02/titles.xlsx
+++ b/data/tags/סינגלים חדשים/sites/mizrahit/2026-03-week02/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L9"/>
+  <dimension ref="A1:L8"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -436,13 +436,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>דניאל חן - נפש תאומה</v>
+        <v>שמעון בר יוחאי - מחרוזת שירי שבת 2026</v>
       </c>
       <c r="B2" t="str">
         <v>2026-03-12</v>
       </c>
       <c r="C2" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409973&amp;sid=9e7b7f175072edda36a8d7e9777610ff</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409980&amp;sid=9645bb93739d54b4055bd94c9f8b39ea</v>
       </c>
       <c r="D2" t="str">
         <v>2026-03-12</v>
@@ -469,18 +469,18 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>דניאל חן - נפש תאומה</v>
+        <v>שמעון בר יוחאי - מחרוזת שירי שבת 2026</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>דנה זר - עוד סיבה</v>
+        <v>שלום ממן - אהלן וסהלן</v>
       </c>
       <c r="B3" t="str">
         <v>2026-03-12</v>
       </c>
       <c r="C3" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409972&amp;sid=9e7b7f175072edda36a8d7e9777610ff</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409979&amp;sid=9645bb93739d54b4055bd94c9f8b39ea</v>
       </c>
       <c r="D3" t="str">
         <v>2026-03-12</v>
@@ -507,18 +507,18 @@
         <v/>
       </c>
       <c r="L3" t="str">
-        <v>דנה זר - עוד סיבה</v>
+        <v>שלום ממן - אהלן וסהלן</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>גל סבג - מחרוזת ברית 2026</v>
+        <v>עומר יונה - הולכת</v>
       </c>
       <c r="B4" t="str">
         <v>2026-03-12</v>
       </c>
       <c r="C4" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409971&amp;sid=9e7b7f175072edda36a8d7e9777610ff</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409978&amp;sid=9645bb93739d54b4055bd94c9f8b39ea</v>
       </c>
       <c r="D4" t="str">
         <v>2026-03-12</v>
@@ -545,18 +545,18 @@
         <v/>
       </c>
       <c r="L4" t="str">
-        <v>גל סבג - מחרוזת ברית 2026</v>
+        <v>עומר יונה - הולכת</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>ג’יין בורדו - חלמתי שאתה פה</v>
+        <v>סער ראסטי - תמונה ישנה</v>
       </c>
       <c r="B5" t="str">
         <v>2026-03-12</v>
       </c>
       <c r="C5" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409970&amp;sid=9e7b7f175072edda36a8d7e9777610ff</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409977&amp;sid=9645bb93739d54b4055bd94c9f8b39ea</v>
       </c>
       <c r="D5" t="str">
         <v>2026-03-12</v>
@@ -583,18 +583,18 @@
         <v/>
       </c>
       <c r="L5" t="str">
-        <v>ג’יין בורדו - חלמתי שאתה פה</v>
+        <v>סער ראסטי - תמונה ישנה</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>ארז יחיאל &amp; אלחנן בידני - כי אשמרה שבת</v>
+        <v>מירי מסיקה - על חוט דק</v>
       </c>
       <c r="B6" t="str">
         <v>2026-03-12</v>
       </c>
       <c r="C6" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409969&amp;sid=9e7b7f175072edda36a8d7e9777610ff</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409976&amp;sid=9645bb93739d54b4055bd94c9f8b39ea</v>
       </c>
       <c r="D6" t="str">
         <v>2026-03-12</v>
@@ -621,18 +621,18 @@
         <v/>
       </c>
       <c r="L6" t="str">
-        <v>ארז יחיאל &amp; אלחנן בידני - כי אשמרה שבת</v>
+        <v>מירי מסיקה - על חוט דק</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>איציק איזמירלי - לא אמרת</v>
+        <v>ליאם אוחיון - הלב שלי</v>
       </c>
       <c r="B7" t="str">
         <v>2026-03-12</v>
       </c>
       <c r="C7" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409968&amp;sid=9e7b7f175072edda36a8d7e9777610ff</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409975&amp;sid=9645bb93739d54b4055bd94c9f8b39ea</v>
       </c>
       <c r="D7" t="str">
         <v>2026-03-12</v>
@@ -659,18 +659,18 @@
         <v/>
       </c>
       <c r="L7" t="str">
-        <v>איציק איזמירלי - לא אמרת</v>
+        <v>ליאם אוחיון - הלב שלי</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>אהרן בלעיש - תודה שאתה כאן</v>
+        <v>ליאור מזרחי &amp; אלירן צורף - אבא גדול</v>
       </c>
       <c r="B8" t="str">
         <v>2026-03-12</v>
       </c>
       <c r="C8" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409967&amp;sid=9e7b7f175072edda36a8d7e9777610ff</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409974&amp;sid=9645bb93739d54b4055bd94c9f8b39ea</v>
       </c>
       <c r="D8" t="str">
         <v>2026-03-12</v>
@@ -697,50 +697,12 @@
         <v/>
       </c>
       <c r="L8" t="str">
-        <v>אהרן בלעיש - תודה שאתה כאן</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="str">
-        <v>אביב סטמס - דמעות על הכרית</v>
-      </c>
-      <c r="B9" t="str">
-        <v>2026-03-12</v>
-      </c>
-      <c r="C9" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409966&amp;sid=9e7b7f175072edda36a8d7e9777610ff</v>
-      </c>
-      <c r="D9" t="str">
-        <v>2026-03-12</v>
-      </c>
-      <c r="E9" t="str">
-        <v/>
-      </c>
-      <c r="F9" t="str">
-        <v/>
-      </c>
-      <c r="G9" t="str">
-        <v/>
-      </c>
-      <c r="H9" t="str">
-        <v/>
-      </c>
-      <c r="I9" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J9" t="str">
-        <v/>
-      </c>
-      <c r="K9" t="str">
-        <v/>
-      </c>
-      <c r="L9" t="str">
-        <v>אביב סטמס - דמעות על הכרית</v>
+        <v>ליאור מזרחי &amp; אלירן צורף - אבא גדול</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L9"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L8"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/tags/סינגלים חדשים/sites/mizrahit/2026-03-week02/titles.xlsx
+++ b/data/tags/סינגלים חדשים/sites/mizrahit/2026-03-week02/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L8"/>
+  <dimension ref="A1:L15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -436,16 +436,16 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>שמעון בר יוחאי - מחרוזת שירי שבת 2026</v>
+        <v>פרחי ירושלים - Ymca</v>
       </c>
       <c r="B2" t="str">
-        <v>2026-03-12</v>
+        <v>2026-03-14</v>
       </c>
       <c r="C2" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409980&amp;sid=9645bb93739d54b4055bd94c9f8b39ea</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410004&amp;sid=0e7672d7a198bf16a3c5dcff7125218d</v>
       </c>
       <c r="D2" t="str">
-        <v>2026-03-12</v>
+        <v>2026-03-14</v>
       </c>
       <c r="E2" t="str">
         <v/>
@@ -469,21 +469,21 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>שמעון בר יוחאי - מחרוזת שירי שבת 2026</v>
+        <v>פרחי ירושלים - Ymca</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>שלום ממן - אהלן וסהלן</v>
+        <v>סיגלית טואטי - שמח ביוון</v>
       </c>
       <c r="B3" t="str">
-        <v>2026-03-12</v>
+        <v>2026-03-14</v>
       </c>
       <c r="C3" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409979&amp;sid=9645bb93739d54b4055bd94c9f8b39ea</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410003&amp;sid=0e7672d7a198bf16a3c5dcff7125218d</v>
       </c>
       <c r="D3" t="str">
-        <v>2026-03-12</v>
+        <v>2026-03-14</v>
       </c>
       <c r="E3" t="str">
         <v/>
@@ -507,21 +507,21 @@
         <v/>
       </c>
       <c r="L3" t="str">
-        <v>שלום ממן - אהלן וסהלן</v>
+        <v>סיגלית טואטי - שמח ביוון</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>עומר יונה - הולכת</v>
+        <v>נשמה וקצב - עכשיו זה נגמר</v>
       </c>
       <c r="B4" t="str">
-        <v>2026-03-12</v>
+        <v>2026-03-14</v>
       </c>
       <c r="C4" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409978&amp;sid=9645bb93739d54b4055bd94c9f8b39ea</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410002&amp;sid=0e7672d7a198bf16a3c5dcff7125218d</v>
       </c>
       <c r="D4" t="str">
-        <v>2026-03-12</v>
+        <v>2026-03-14</v>
       </c>
       <c r="E4" t="str">
         <v/>
@@ -545,21 +545,21 @@
         <v/>
       </c>
       <c r="L4" t="str">
-        <v>עומר יונה - הולכת</v>
+        <v>נשמה וקצב - עכשיו זה נגמר</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>סער ראסטי - תמונה ישנה</v>
+        <v>משה ברששת - Zina Cover</v>
       </c>
       <c r="B5" t="str">
-        <v>2026-03-12</v>
+        <v>2026-03-14</v>
       </c>
       <c r="C5" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409977&amp;sid=9645bb93739d54b4055bd94c9f8b39ea</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410001&amp;sid=0e7672d7a198bf16a3c5dcff7125218d</v>
       </c>
       <c r="D5" t="str">
-        <v>2026-03-12</v>
+        <v>2026-03-14</v>
       </c>
       <c r="E5" t="str">
         <v/>
@@ -583,21 +583,21 @@
         <v/>
       </c>
       <c r="L5" t="str">
-        <v>סער ראסטי - תמונה ישנה</v>
+        <v>משה ברששת - Zina Cover</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>מירי מסיקה - על חוט דק</v>
+        <v>מאיר חג'בי - היום</v>
       </c>
       <c r="B6" t="str">
-        <v>2026-03-12</v>
+        <v>2026-03-14</v>
       </c>
       <c r="C6" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409976&amp;sid=9645bb93739d54b4055bd94c9f8b39ea</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410000&amp;sid=0e7672d7a198bf16a3c5dcff7125218d</v>
       </c>
       <c r="D6" t="str">
-        <v>2026-03-12</v>
+        <v>2026-03-14</v>
       </c>
       <c r="E6" t="str">
         <v/>
@@ -621,21 +621,21 @@
         <v/>
       </c>
       <c r="L6" t="str">
-        <v>מירי מסיקה - על חוט דק</v>
+        <v>מאיר חג'בי - היום</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>ליאם אוחיון - הלב שלי</v>
+        <v>לידור עמירה - שמעתי שהבית חרב</v>
       </c>
       <c r="B7" t="str">
-        <v>2026-03-12</v>
+        <v>2026-03-14</v>
       </c>
       <c r="C7" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409975&amp;sid=9645bb93739d54b4055bd94c9f8b39ea</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409999&amp;sid=0e7672d7a198bf16a3c5dcff7125218d</v>
       </c>
       <c r="D7" t="str">
-        <v>2026-03-12</v>
+        <v>2026-03-14</v>
       </c>
       <c r="E7" t="str">
         <v/>
@@ -659,50 +659,316 @@
         <v/>
       </c>
       <c r="L7" t="str">
-        <v>ליאם אוחיון - הלב שלי</v>
+        <v>לידור עמירה - שמעתי שהבית חרב</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>ליאור מזרחי &amp; אלירן צורף - אבא גדול</v>
+        <v>לידור עמירה - כמה אהבה עצמית</v>
       </c>
       <c r="B8" t="str">
+        <v>2026-03-14</v>
+      </c>
+      <c r="C8" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409998&amp;sid=0e7672d7a198bf16a3c5dcff7125218d</v>
+      </c>
+      <c r="D8" t="str">
+        <v>2026-03-14</v>
+      </c>
+      <c r="E8" t="str">
+        <v/>
+      </c>
+      <c r="F8" t="str">
+        <v/>
+      </c>
+      <c r="G8" t="str">
+        <v/>
+      </c>
+      <c r="H8" t="str">
+        <v/>
+      </c>
+      <c r="I8" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J8" t="str">
+        <v/>
+      </c>
+      <c r="K8" t="str">
+        <v/>
+      </c>
+      <c r="L8" t="str">
+        <v>לידור עמירה - כמה אהבה עצמית</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>יוסף חיים - בובה על חוט</v>
+      </c>
+      <c r="B9" t="str">
+        <v>2026-03-14</v>
+      </c>
+      <c r="C9" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409997&amp;sid=0e7672d7a198bf16a3c5dcff7125218d</v>
+      </c>
+      <c r="D9" t="str">
+        <v>2026-03-14</v>
+      </c>
+      <c r="E9" t="str">
+        <v/>
+      </c>
+      <c r="F9" t="str">
+        <v/>
+      </c>
+      <c r="G9" t="str">
+        <v/>
+      </c>
+      <c r="H9" t="str">
+        <v/>
+      </c>
+      <c r="I9" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J9" t="str">
+        <v/>
+      </c>
+      <c r="K9" t="str">
+        <v/>
+      </c>
+      <c r="L9" t="str">
+        <v>יוסף חיים - בובה על חוט</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>Pure Spirit - תן לנו כח - גרסת שאגת הארי</v>
+      </c>
+      <c r="B10" t="str">
+        <v>2026-03-14</v>
+      </c>
+      <c r="C10" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409996&amp;sid=0e7672d7a198bf16a3c5dcff7125218d</v>
+      </c>
+      <c r="D10" t="str">
+        <v>2026-03-14</v>
+      </c>
+      <c r="E10" t="str">
+        <v/>
+      </c>
+      <c r="F10" t="str">
+        <v/>
+      </c>
+      <c r="G10" t="str">
+        <v/>
+      </c>
+      <c r="H10" t="str">
+        <v/>
+      </c>
+      <c r="I10" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J10" t="str">
+        <v/>
+      </c>
+      <c r="K10" t="str">
+        <v/>
+      </c>
+      <c r="L10" t="str">
+        <v>Pure Spirit - תן לנו כח - גרסת שאגת הארי</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>אלעד מרגי - שוב</v>
+      </c>
+      <c r="B11" t="str">
+        <v>2026-03-14</v>
+      </c>
+      <c r="C11" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409995&amp;sid=0e7672d7a198bf16a3c5dcff7125218d</v>
+      </c>
+      <c r="D11" t="str">
+        <v>2026-03-14</v>
+      </c>
+      <c r="E11" t="str">
+        <v/>
+      </c>
+      <c r="F11" t="str">
+        <v/>
+      </c>
+      <c r="G11" t="str">
+        <v/>
+      </c>
+      <c r="H11" t="str">
+        <v/>
+      </c>
+      <c r="I11" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J11" t="str">
+        <v/>
+      </c>
+      <c r="K11" t="str">
+        <v/>
+      </c>
+      <c r="L11" t="str">
+        <v>אלעד מרגי - שוב</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>יוסף חיים - הלוואי</v>
+      </c>
+      <c r="B12" t="str">
+        <v>2026-03-14</v>
+      </c>
+      <c r="C12" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409994&amp;sid=0e7672d7a198bf16a3c5dcff7125218d</v>
+      </c>
+      <c r="D12" t="str">
+        <v>2026-03-14</v>
+      </c>
+      <c r="E12" t="str">
+        <v/>
+      </c>
+      <c r="F12" t="str">
+        <v/>
+      </c>
+      <c r="G12" t="str">
+        <v/>
+      </c>
+      <c r="H12" t="str">
+        <v/>
+      </c>
+      <c r="I12" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J12" t="str">
+        <v/>
+      </c>
+      <c r="K12" t="str">
+        <v/>
+      </c>
+      <c r="L12" t="str">
+        <v>יוסף חיים - הלוואי</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>דורין פסטרנק - משחקים של כבוד</v>
+      </c>
+      <c r="B13" t="str">
+        <v>2026-03-14</v>
+      </c>
+      <c r="C13" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409993&amp;sid=0e7672d7a198bf16a3c5dcff7125218d</v>
+      </c>
+      <c r="D13" t="str">
+        <v>2026-03-14</v>
+      </c>
+      <c r="E13" t="str">
+        <v/>
+      </c>
+      <c r="F13" t="str">
+        <v/>
+      </c>
+      <c r="G13" t="str">
+        <v/>
+      </c>
+      <c r="H13" t="str">
+        <v/>
+      </c>
+      <c r="I13" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J13" t="str">
+        <v/>
+      </c>
+      <c r="K13" t="str">
+        <v/>
+      </c>
+      <c r="L13" t="str">
+        <v>דורין פסטרנק - משחקים של כבוד</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="str">
+        <v>אביב לוסב - התנשאי לי</v>
+      </c>
+      <c r="B14" t="str">
+        <v>2026-03-14</v>
+      </c>
+      <c r="C14" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409992&amp;sid=0e7672d7a198bf16a3c5dcff7125218d</v>
+      </c>
+      <c r="D14" t="str">
+        <v>2026-03-14</v>
+      </c>
+      <c r="E14" t="str">
+        <v/>
+      </c>
+      <c r="F14" t="str">
+        <v/>
+      </c>
+      <c r="G14" t="str">
+        <v/>
+      </c>
+      <c r="H14" t="str">
+        <v/>
+      </c>
+      <c r="I14" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J14" t="str">
+        <v/>
+      </c>
+      <c r="K14" t="str">
+        <v/>
+      </c>
+      <c r="L14" t="str">
+        <v>אביב לוסב - התנשאי לי</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="str">
+        <v>דניאל חן - נפש תאומה קאבר</v>
+      </c>
+      <c r="B15" t="str">
         <v>2026-03-12</v>
       </c>
-      <c r="C8" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409974&amp;sid=9645bb93739d54b4055bd94c9f8b39ea</v>
-      </c>
-      <c r="D8" t="str">
-        <v>2026-03-12</v>
-      </c>
-      <c r="E8" t="str">
-        <v/>
-      </c>
-      <c r="F8" t="str">
-        <v/>
-      </c>
-      <c r="G8" t="str">
-        <v/>
-      </c>
-      <c r="H8" t="str">
-        <v/>
-      </c>
-      <c r="I8" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J8" t="str">
-        <v/>
-      </c>
-      <c r="K8" t="str">
-        <v/>
-      </c>
-      <c r="L8" t="str">
-        <v>ליאור מזרחי &amp; אלירן צורף - אבא גדול</v>
+      <c r="C15" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409973&amp;sid=0e7672d7a198bf16a3c5dcff7125218d</v>
+      </c>
+      <c r="D15" t="str">
+        <v>2026-03-14</v>
+      </c>
+      <c r="E15" t="str">
+        <v/>
+      </c>
+      <c r="F15" t="str">
+        <v/>
+      </c>
+      <c r="G15" t="str">
+        <v/>
+      </c>
+      <c r="H15" t="str">
+        <v/>
+      </c>
+      <c r="I15" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J15" t="str">
+        <v/>
+      </c>
+      <c r="K15" t="str">
+        <v/>
+      </c>
+      <c r="L15" t="str">
+        <v>דניאל חן - נפש תאומה קאבר</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L8"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L15"/>
   </ignoredErrors>
 </worksheet>
 </file>